--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260624.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260624.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D95"/>
+  <dimension ref="A1:D96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -887,17 +887,17 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3481</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>群創</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>1,975,288</t>
+          <t>12,706,134</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -909,17 +909,17 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>3481</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>群創</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>12,706,134</t>
+          <t>1,975,288</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>845,349</t>
+          <t>139,482</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1085,17 +1085,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>139,482</t>
+          <t>845,349</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>570,000</t>
+          <t>44,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>44,000</t>
+          <t>570,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>和碩</t>
+          <t>華新科</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>3,434,981</t>
+          <t>491,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>華新科</t>
+          <t>和碩</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>491,000</t>
+          <t>3,434,981</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>仁寶</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>7,074,249</t>
+          <t>2,562,703</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>仁寶</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>2,562,703</t>
+          <t>7,074,249</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1657,17 +1657,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>766,000</t>
+          <t>179,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1679,17 +1679,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>179,000</t>
+          <t>766,000</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>202607WVHFN6F</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>富邦科技ETF期貨</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>2,161,107</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1723,17 +1723,17 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>202607WVHFN6F</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>富邦科技ETF期貨</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>2,161,107</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -1745,17 +1745,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>4,894,956</t>
+          <t>92,000</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -1767,17 +1767,17 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>1,169,076</t>
+          <t>794,000</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -1789,17 +1789,17 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>794,000</t>
+          <t>4,894,956</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -1811,17 +1811,17 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>92,000</t>
+          <t>1,169,076</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -1833,17 +1833,17 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>113,000</t>
+          <t>286,000</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -1855,17 +1855,17 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>286,000</t>
+          <t>113,000</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -1921,17 +1921,17 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>990,121</t>
+          <t>384,000</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -1943,17 +1943,17 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>6213</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>384,000</t>
+          <t>990,121</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -1965,17 +1965,17 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>168,000</t>
+          <t>176,000</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -1987,17 +1987,17 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>64,538</t>
+          <t>168,000</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -2009,17 +2009,17 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>155,000</t>
+          <t>64,538</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -2031,17 +2031,17 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>327,000</t>
+          <t>155,000</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -2053,17 +2053,17 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>鴻準</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>1,734,000</t>
+          <t>327,000</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -2075,17 +2075,17 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>鴻準</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>176,000</t>
+          <t>1,734,000</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -2119,17 +2119,17 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>4919</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>新唐</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>331,000</t>
+          <t>671,000</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -2141,17 +2141,17 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>4919</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>新唐</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>671,000</t>
+          <t>331,000</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -2163,17 +2163,17 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>6526</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>台勝科</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>71,000</t>
+          <t>113,000</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
@@ -2185,17 +2185,17 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>6526</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>台勝科</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>113,000</t>
+          <t>71,000</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -2239,6 +2239,24 @@
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>RDI_NTD</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>-198,201,402</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
